--- a/artfynd/A 23023-2026 artfynd.xlsx
+++ b/artfynd/A 23023-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130962542</v>
+        <v>130962481</v>
       </c>
       <c r="B2" t="n">
-        <v>93138</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562635</v>
+        <v>562489</v>
       </c>
       <c r="R2" t="n">
-        <v>6730725</v>
+        <v>6730682</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130962541</v>
+        <v>130962529</v>
       </c>
       <c r="B3" t="n">
-        <v>98935</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562560</v>
+        <v>562592</v>
       </c>
       <c r="R3" t="n">
-        <v>6730731</v>
+        <v>6730472</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130962531</v>
+        <v>130962530</v>
       </c>
       <c r="B4" t="n">
-        <v>97883</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562526</v>
+        <v>562542</v>
       </c>
       <c r="R4" t="n">
-        <v>6730656</v>
+        <v>6730480</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130962530</v>
+        <v>130962542</v>
       </c>
       <c r="B5" t="n">
-        <v>93138</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562542</v>
+        <v>562635</v>
       </c>
       <c r="R5" t="n">
-        <v>6730480</v>
+        <v>6730725</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130962529</v>
+        <v>130962477</v>
       </c>
       <c r="B6" t="n">
-        <v>93138</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562592</v>
+        <v>562623</v>
       </c>
       <c r="R6" t="n">
-        <v>6730472</v>
+        <v>6730334</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130962481</v>
+        <v>130962539</v>
       </c>
       <c r="B7" t="n">
-        <v>93138</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562489</v>
+        <v>562507</v>
       </c>
       <c r="R7" t="n">
-        <v>6730682</v>
+        <v>6730738</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,6 +1284,720 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130962528</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562559</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6730410</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130962537</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562466</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6730687</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130962538</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562479</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6730718</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130962541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562560</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6730731</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130962531</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562526</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6730656</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130962540</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562549</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6730749</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130962518</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562669</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6730448</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23023-2026 artfynd.xlsx
+++ b/artfynd/A 23023-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962530</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962477</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962539</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962528</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962537</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962538</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962541</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962531</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962540</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,8 +2063,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>